--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-rtos-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-rtos-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Trong kiến trúc ARM Cortex-M, độ ưu tiên ngắt nhỏ hơn nghĩa là ưu tiên cao hơn. FreeRTOS định nghĩa `configMAX_SYSCALL_INTERRUPT_PRIORITY` (ngưỡng ngắt an toàn hệ điều hành). Các ngắt phần cứng có ưu tiên cao hơn ngưỡng này không bị RTOS trì hoãn (đáp ứng cực nhanh), nhưng tuyệt đối không được gọi bất kỳ API RTOS nào vì chúng không được bảo vệ bởi critical sections của RTOS, gây hỏng cấu trúc dữ liệu kernel dẫn đến HardFault.</v>
       </c>
       <c r="F2" t="str">
+        <v>Hàm `xQueueSendFromISR` bắt buộc phải được gọi bằng ngôn ngữ lập trình Assembly thay vì C nhúng — giới hạn ngôn ngữ gọi API</v>
+      </c>
+      <c r="G2" t="str">
+        <v>FreeRTOS cấm tuyệt đối việc gửi bất kỳ bản tin nào từ ngắt vào Message Queue — cấm gửi tin nhắn từ ngắt</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Ngắt UART sử dụng chung một thanh ghi dịch dữ liệu với cổng nạp SWD của chip — trùng lặp thanh ghi ngoại vi</v>
+      </c>
+      <c r="I2" t="str">
         <v>Ngắt UART được cấu hình độ ưu tiên phần cứng cao hơn (giá trị priority nhỏ hơn) so với cấu hình `configMAX_SYSCALL_INTERRUPT_PRIORITY` của FreeRTOS, dẫn đến việc gọi API RTOS từ ngắt bị cấm — phân quyền ngắt phần cứng vượt ngưỡng syscall</v>
       </c>
-      <c r="G2" t="str">
-        <v>Ngắt UART sử dụng chung một thanh ghi dịch dữ liệu với cổng nạp SWD của chip — trùng lặp thanh ghi ngoại vi</v>
-      </c>
-      <c r="H2" t="str">
-        <v>FreeRTOS cấm tuyệt đối việc gửi bất kỳ bản tin nào từ ngắt vào Message Queue — cấm gửi tin nhắn từ ngắt</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Hàm `xQueueSendFromISR` bắt buộc phải được gọi bằng ngôn ngữ lập trình Assembly thay vì C nhúng — giới hạn ngôn ngữ gọi API</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Đưa toàn bộ thuật toán điều khiển động cơ vào chạy trực tiếp trong một Timer Interrupt phần cứng có độ ưu tiên cao nhất, chỉ đẩy dữ liệu trạng thái qua DMA/Queue về RTOS task để xử lý giám sát và hiển thị sau — tách biệt luồng điều khiển cứng vào ngắt phần cứng</v>
       </c>
       <c r="G3" t="str">
+        <v>Tăng tần số xung nhịp hệ thống (SysTick Rate) của RTOS lên mức 100 kHz để tăng độ chính xác của scheduler — tăng SysTick rate quá tải CPU</v>
+      </c>
+      <c r="H3" t="str">
         <v>Tạo một RTOS task có độ ưu tiên cao nhất và sử dụng hàm `vTaskDelay(1)` để định thời chu kỳ điều khiển động cơ — định thời task RTOS rủi ro trễ</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Chạy hệ thống ở chế độ Cooperative Scheduling để các task tự chia sẻ CPU một cách hoàn hảo — cooperative scheduling không đảm bảo</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Tăng tần số xung nhịp hệ thống (SysTick Rate) của RTOS lên mức 100 kHz để tăng độ chính xác của scheduler — tăng SysTick rate quá tải CPU</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -527,10 +527,10 @@
         <v>Gán cho mỗi tài nguyên dùng chung một độ ưu tiên trần (bằng độ ưu tiên cao nhất của task có thể dùng nó). Khi một task giữ khóa tài nguyên, nó tự động được nâng độ ưu tiên lên bằng độ ưu tiên trần này — nâng độ ưu tiên lên mức trần tài nguyên</v>
       </c>
       <c r="G4" t="str">
+        <v>Cấu hình cho hệ điều hành tự động chạy lại từ đầu khi phát hiện có tranh chấp tài nguyên xảy ra — tự động reset hệ thống</v>
+      </c>
+      <c r="H4" t="str">
         <v>Ngăn chặn hoàn toàn việc các task có độ ưu tiên khác nhau được phép truy cập vào cùng một tài nguyên — ngăn chặn truy cập chéo</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Cấu hình cho hệ điều hành tự động chạy lại từ đầu khi phát hiện có tranh chấp tài nguyên xảy ra — tự động reset hệ thống</v>
       </c>
       <c r="I4" t="str">
         <v>Yêu cầu lập trình viên không được phép sử dụng bất kỳ từ khóa Mutex hay Semaphore nào trong code — cấm dùng khóa</v>
@@ -556,19 +556,19 @@
         <v>`heap_1.c` chỉ cho malloc không cho free (thích hợp hệ thống khởi tạo 1 lần). `heap_2.c` cho free nhưng không ghép các khối trống nhỏ cạnh nhau lại thành khối lớn, chạy lâu năm sẽ bị phân mảnh (Fragmentation) dẫn đến việc `pvPortMalloc` báo lỗi hết bộ nhớ dù tổng RAM trống vẫn đủ. `heap_4.c` giải quyết triệt để bằng cách gộp các khối trống liền kề.</v>
       </c>
       <c r="F5" t="str">
+        <v>Vì `heap_4.c` hoàn toàn miễn phí còn các file heap khác bắt buộc phải mua bản quyền thương mại — bản quyền file heap</v>
+      </c>
+      <c r="G5" t="str">
         <v>Vì `heap_4.c` áp dụng thuật toán ghép các khối bộ nhớ trống kề nhau (Coalescing) để ngăn chặn hiện tượng phân mảnh bộ nhớ (Memory Fragmentation); `heap_1.c` không cho phép giải phóng, `heap_2.c` giải phóng nhưng không ghép khối — chống phân mảnh bộ nhớ ghép khối kề nhau</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
+        <v>Vì `heap_4.c` chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip</v>
+      </c>
+      <c r="I5" t="str">
         <v>Vì `heap_4.c` tự động nén dữ liệu lưu trên RAM sang bộ nhớ Flash khi tắt nguồn điện — nén dữ liệu Flash</v>
       </c>
-      <c r="H5" t="str">
-        <v>Vì `heap_4.c` hoàn toàn miễn phí còn các file heap khác bắt buộc phải mua bản quyền thương mại — bản quyền file heap</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Vì `heap_4.c` chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Mặc định, ngắt SysTick xảy ra sau mỗi 1ms để cập nhật RTOS tick, điều này liên tục đánh thức chip dậy khỏi chế độ ngủ (Sleep Mode), gây hao pin. Tickless Idle tính toán xem task Ready tiếp theo sẽ chạy sau bao lâu (ví dụ 50ms nữa), sau đó cấu hình bộ hẹn giờ đánh thức và tắt ngắt SysTick, cho phép chip ngủ sâu liên tục trong 50ms.</v>
       </c>
       <c r="F6" t="str">
+        <v>Hệ điều hành tự động ngắt kết nối nguồn điện cấp cho toàn bộ các thiết bị ngoại vi cảm biến bên ngoài chip — ngắt nguồn ngoại vi</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Hệ điều hành bắt buộc lập trình viên phải rút mạch nạp chương trình ra khỏi chip khi đang chạy — rút mạch nạp</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Hệ điều hành tự động giảm tần số hoạt động của thạch anh ngoại vi xuống còn 1 Hz — giảm tần số thạch anh ngoại vi</v>
+      </c>
+      <c r="I6" t="str">
         <v>Hệ điều hành tạm thời dừng ngắt SysTick phần cứng khi hệ thống rảnh rỗi, cấu hình Timer phần cứng để đánh thức chip sau một khoảng thời gian dài ngủ sâu tương ứng với thời gian rảnh dự kiến — tắt ngắt SysTick định thời ngủ sâu</v>
       </c>
-      <c r="G6" t="str">
-        <v>Hệ điều hành tự động giảm tần số hoạt động của thạch anh ngoại vi xuống còn 1 Hz — giảm tần số thạch anh ngoại vi</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Hệ điều hành tự động ngắt kết nối nguồn điện cấp cho toàn bộ các thiết bị ngoại vi cảm biến bên ngoài chip — ngắt nguồn ngoại vi</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Hệ điều hành bắt buộc lập trình viên phải rút mạch nạp chương trình ra khỏi chip khi đang chạy — rút mạch nạp</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Task Notifications gửi tín hiệu trực tiếp vào TCB (Task Control Block) của task đích, chạy cực nhanh và không tốn RAM khởi tạo đối tượng độc lập. Event Groups là công cụ đồng bộ hóa mạnh mẽ, cho phép một task bị block cho đến khi toàn bộ các sự kiện mong muốn xảy ra (ví dụ: Task chỉ chạy khi cả 3 sự kiện Wifi connected AND Sensor read AND Flash ready đều tích cờ).</v>
       </c>
       <c r="F7" t="str">
+        <v>Task Notifications chỉ dùng cho dữ liệu số nguyên; còn Event Groups chỉ dùng cho kiểu dữ liệu chuỗi — kiểu dữ liệu truyền</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Task Notifications bắt buộc phải viết bằng ngôn ngữ Assembly; còn Event Groups viết bằng ngôn ngữ C — giới hạn ngôn ngữ code</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Task Notifications chỉ chạy trên môi trường giả lập; còn Event Groups chạy trên chip thực tế — phân loại môi trường chạy</v>
+      </c>
+      <c r="I7" t="str">
         <v>Task Notifications truyền tín hiệu trực tiếp đến một task cụ thể (nhanh hơn, tốn ít RAM hơn); Event Groups cho phép đồng bộ hóa nhiều task dựa trên tổ hợp nhiều sự kiện (AND/OR logic) — signaling đơn mục tiêu vs đồng bộ hóa đa sự kiện phức tạp</v>
       </c>
-      <c r="G7" t="str">
-        <v>Task Notifications chỉ dùng cho dữ liệu số nguyên; còn Event Groups chỉ dùng cho kiểu dữ liệu chuỗi — kiểu dữ liệu truyền</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Task Notifications bắt buộc phải viết bằng ngôn ngữ Assembly; còn Event Groups viết bằng ngôn ngữ C — giới hạn ngôn ngữ code</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Task Notifications chỉ chạy trên môi trường giả lập; còn Event Groups chạy trên chip thực tế — phân loại môi trường chạy</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Trong kiến trúc ARM Cortex-M, FreeRTOS sử dụng thanh ghi `BASEPRI` để che (mask) các ngắt có độ ưu tiên thấp hơn SysTick khi chạy critical sections. Lỗi treo ở `vPortRaiseBASEPRI` thường do cấu hình sai nhóm ưu tiên ngắt (`NVIC_PriorityGroupConfig(NVIC_PriorityGroup_4)` không được gọi), dẫn đến việc tính toán mức ưu tiên của RTOS bị sai lệch gây lỗi Assert treo chip.</v>
       </c>
       <c r="F8" t="str">
+        <v>Đường dây bus truyền dữ liệu I2C ngoại vi bị chập mạch vật lý xuống đất — chập dây bus phần cứng</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Cầu chì bảo vệ chống đọc mã nguồn của con chip vi điều khiển đã bị kích hoạt — bảo vệ chống đọc code</v>
+      </c>
+      <c r="H8" t="str">
         <v>Hệ thống bị treo do một ngắt có priority cao hơn SysTick gọi một API RTOS thông thường hoặc xảy ra xung đột cấu hình phân nhóm ưu tiên ngắt (Priority Grouping) trên ARM Cortex-M — xung đột cấu hình priority grouping ngắt</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>Vi điều khiển bị hết dung lượng bộ nhớ Flash để lưu trữ mã nguồn chương trình — hết bộ nhớ Flash</v>
       </c>
-      <c r="H8" t="str">
-        <v>Cầu chì bảo vệ chống đọc mã nguồn của con chip vi điều khiển đã bị kích hoạt — bảo vệ chống đọc code</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Đường dây bus truyền dữ liệu I2C ngoại vi bị chập mạch vật lý xuống đất — chập dây bus phần cứng</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Trong các hệ thống y tế/hàng không, tính xác định (Determinism) là tuyệt đối. Việc malloc bộ nhớ động lúc đang chạy có thể thất bại nếu heap bị phân mảnh. Sử dụng các API `Static` (như `xTaskCreateStatic`, `xQueueCreateStatic`) yêu cầu lập trình viên khai báo sẵn vùng đệm buffer tĩnh (static arrays) từ trước, bộ nhớ được cấp phát và kiểm tra an toàn ngay khi biên dịch (compile-time), triệt tiêu rủi ro thiếu RAM lúc chạy.</v>
       </c>
       <c r="F9" t="str">
+        <v>Vì cấp phát tĩnh làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với cấp phát động — sinh nhiệt phần cứng</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Vì chuẩn MISRA C cấm tuyệt đối việc sử dụng bất kỳ hàng đợi Message Queue nào trong lập trình nhúng — cấm sử dụng hàng đợi</v>
+      </c>
+      <c r="H9" t="str">
         <v>Vì cấp phát động tại Runtime có rủi ro cạn kiệt bộ nhớ Heap (Out-of-memory) hoặc phân mảnh bộ nhớ dẫn đến sập hệ thống bất ngờ; Giải pháp: Sử dụng các API cấp phát tĩnh (như `xQueueCreateStatic()`) tại thời điểm biên dịch — cấp phát tĩnh an toàn MISRA C</v>
       </c>
-      <c r="G9" t="str">
-        <v>Vì cấp phát tĩnh làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với cấp phát động — sinh nhiệt phần cứng</v>
-      </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Vì cấp phát tĩnh bắt buộc phải sử dụng nguồn điện pin 9V thay vì nguồn USB 5V — ràng buộc nguồn điện vật lý</v>
       </c>
-      <c r="I9" t="str">
-        <v>Vì chuẩn MISRA C cấm tuyệt đối việc sử dụng bất kỳ hàng đợi Message Queue nào trong lập trình nhúng — cấm sử dụng hàng đợi</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Trong Cooperative, ngắt SysTick vẫn xảy ra nhưng không kích hoạt scheduler chuyển đổi ngữ cảnh. Task thấp đang chạy sẽ không bị cướp quyền bởi task cao vừa Ready. Nếu task thấp bị lỗi Loop vô hạn mà không gọi `taskYIELD()`, hệ thống sẽ bị treo cứng các tác vụ khác. Chế độ này ít được dùng trừ khi hệ thống có tài nguyên cực kỳ hạn chế.</v>
       </c>
       <c r="F10" t="str">
+        <v>Cooperative: Hệ điều hành tự động xóa bỏ các task có thời gian chạy quá 5 giây — tự động xóa task chạy lâu</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Cooperative: Tiết kiệm dung lượng bộ nhớ Flash lưu trữ code hơn so với Preemptive — tối ưu dung lượng Flash</v>
+      </c>
+      <c r="H10" t="str">
         <v>Cooperative: Task chỉ nhường CPU khi tự nguyện gọi hàm yield hoặc block; rủi ro lớn nhất là một task chạy vòng lặp vô hạn (không nhường) sẽ chiếm dụng CPU vĩnh viễn làm treo toàn bộ các task khác — task không tự nguyện nhường làm treo hệ thống</v>
       </c>
-      <c r="G10" t="str">
-        <v>Cooperative: Hệ điều hành tự động xóa bỏ các task có thời gian chạy quá 5 giây — tự động xóa task chạy lâu</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Cooperative: Bắt buộc tất cả các task phải có cùng một mức độ ưu tiên bằng nhau — đồng bộ độ ưu tiên</v>
       </c>
-      <c r="I10" t="str">
-        <v>Cooperative: Tiết kiệm dung lượng bộ nhớ Flash lưu trữ code hơn so với Preemptive — tối ưu dung lượng Flash</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Trên chip đơn nhân, critical section chỉ cần tắt ngắt là đủ bảo vệ (vì không có luồng nào khác có thể chạy). Trên chip đa nhân (Symmetric Multiprocessing - SMP), việc tắt ngắt ở Nhân 1 không thể ngăn cản Nhân 2 (vẫn đang chạy bình thường) ghi vào biến dùng chung. Ta phải sử dụng cơ chế Spinlock (khóa xoay vòng phần cứng) kết hợp tắt ngắt nội bộ để bảo vệ an toàn tài nguyên.</v>
       </c>
       <c r="F11" t="str">
+        <v>Yêu cầu hai nhân vật lý tự động đồng bộ hóa xung nhịp hoạt động chênh lệch nhau đúng 90 độ — đồng bộ xung lệch pha</v>
+      </c>
+      <c r="G11" t="str">
         <v>Sử dụng cơ chế khóa Spinlock kết hợp với Mutex đa nhân (như `portMUX_TYPE` mux) để khóa tài nguyên xuyên nhân, ngăn cản nhân này ghi khi nhân kia đang truy cập — Spinlock khóa đa nhân an toàn</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Chỉ cần khai báo biến toàn cục đó với từ khóa `volatile` là đủ đảm bảo an toàn truy cập song song — volatile không đủ an toàn ngắt đa nhân</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Sử dụng cơ chế tắt ngắt toàn cục của nhân 1 để tự động tắt ngắt của nhân 2 — tắt ngắt chéo nhân không hỗ trợ trực tiếp</v>
       </c>
-      <c r="I11" t="str">
-        <v>Yêu cầu hai nhân vật lý tự động đồng bộ hóa xung nhịp hoạt động chênh lệch nhau đúng 90 độ — đồng bộ xung lệch pha</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
